--- a/artfynd/A 25957-2024 artfynd.xlsx
+++ b/artfynd/A 25957-2024 artfynd.xlsx
@@ -3447,7 +3447,7 @@
         <v>118996196</v>
       </c>
       <c r="B26" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
